--- a/app/ml/dataset/PCOS_data_without_infertility.xlsx
+++ b/app/ml/dataset/PCOS_data_without_infertility.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RESHAM\Downloads\archive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f58a5fe19981fb21/Desktop/programs/pcos_Copy/PCOS/app/ml/dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99120D4D-6846-4E2F-8856-6C96A7E46AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{99120D4D-6846-4E2F-8856-6C96A7E46AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{300DCD16-8EEE-4FB5-A0FE-B8DCDEC096EE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Full_new" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Full_new!$C$1:$C$1000</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -540,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AS1000"/>
@@ -75098,465 +75101,472 @@
       </c>
       <c r="AS542" s="1"/>
     </row>
-    <row r="543" spans="1:45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" spans="1:45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" spans="1:45" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" spans="1:45" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <autoFilter ref="C1:C1000" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="0">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>